--- a/data/bb-templates/wf-blue-owl.xlsx
+++ b/data/bb-templates/wf-blue-owl.xlsx
@@ -132,25 +132,25 @@
     <t>A. Rated Investors</t>
   </si>
   <si>
-    <t>Rated Included</t>
+    <t>Included Investors (Rated)</t>
   </si>
   <si>
     <t>B. Unrated Investors</t>
   </si>
   <si>
-    <t>Non-Rated Included</t>
+    <t>Included Investors (Non-Rated)</t>
   </si>
   <si>
     <t>C. Eligible Investors</t>
   </si>
   <si>
-    <t>Designated Institutional</t>
+    <t>Insitutional Designated Investors</t>
   </si>
   <si>
     <t>D. Excluded Investors</t>
   </si>
   <si>
-    <t>Ineligible Investors</t>
+    <t>Excluded Investors</t>
   </si>
   <si>
     <t>tab_sort</t>
@@ -239,7 +239,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +250,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -283,13 +289,13 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -808,7 +814,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -822,7 +828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -836,7 +842,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -850,7 +856,7 @@
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
